--- a/site-src/examples/owlplanner/HFP_kim+sam.xlsx
+++ b/site-src/examples/owlplanner/HFP_kim+sam.xlsx
@@ -1741,7 +1741,7 @@
         <v>520000</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>2038</v>
